--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_advanced_features.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_advanced_features.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\assumptions\VerveStacks_ISO_template\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B6907D-6C39-452D-B64B-38F32025EB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD731D8E-C82B-474A-B20B-FDB65B37156B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
   </bookViews>
   <sheets>
     <sheet name="veda input" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="280">
   <si>
     <t>ACT_MINLD</t>
   </si>
@@ -2861,10 +2861,10 @@
     <t>DEF_C</t>
   </si>
   <si>
-    <t>Gas Turbine*</t>
-  </si>
-  <si>
     <t/>
+  </si>
+  <si>
+    <t>en_gas_turbine_*</t>
   </si>
 </sst>
 </file>
@@ -2996,7 +2996,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
@@ -3037,9 +3037,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
@@ -4306,49 +4303,50 @@
       </c>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.45">
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="15">
         <v>0</v>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="15">
         <v>0.5</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="15">
         <v>1.2</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="15">
         <v>0.01</v>
       </c>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="23" t="s">
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" t="s">
+        <v>279</v>
+      </c>
+      <c r="L18" s="20">
+        <v>30</v>
+      </c>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="O18" s="15">
+        <v>1.2</v>
+      </c>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="L18" s="23">
-        <v>30</v>
-      </c>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22">
-        <v>0.5</v>
-      </c>
-      <c r="O18" s="22">
-        <v>1.2</v>
-      </c>
-      <c r="P18" s="22"/>
-      <c r="Q18" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="R18" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="S18" s="22" t="s">
+      <c r="R18" s="15" t="s">
         <v>278</v>
+      </c>
+      <c r="S18" s="15" t="str">
+        <f>K18</f>
+        <v>en_gas_turbine_*</v>
       </c>
     </row>
   </sheetData>
@@ -4385,7 +4383,7 @@
     <col min="24" max="24" width="5" bestFit="1" customWidth="1"/>
     <col min="25" max="26" width="6" bestFit="1" customWidth="1"/>
     <col min="27" max="28" width="4" bestFit="1" customWidth="1"/>
-    <col min="29" max="34" width="4" style="20" customWidth="1"/>
+    <col min="29" max="34" width="4" customWidth="1"/>
     <col min="36" max="36" width="14.53125" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="1.73046875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="4.73046875" bestFit="1" customWidth="1"/>
@@ -4472,71 +4470,71 @@
         <f>P3+1</f>
         <v>61</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3">
         <f>Q3+18</f>
         <v>79</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3">
         <f>R3+1</f>
         <v>80</v>
       </c>
-      <c r="T3" s="20">
+      <c r="T3">
         <f>S3+1</f>
         <v>81</v>
       </c>
-      <c r="U3" s="20">
+      <c r="U3">
         <f>T3+18</f>
         <v>99</v>
       </c>
-      <c r="V3" s="20">
+      <c r="V3">
         <f>U3+1</f>
         <v>100</v>
       </c>
-      <c r="W3" s="20">
+      <c r="W3">
         <f>V3+1</f>
         <v>101</v>
       </c>
-      <c r="X3" s="20">
+      <c r="X3">
         <f>W3+18</f>
         <v>119</v>
       </c>
-      <c r="Y3" s="20">
+      <c r="Y3">
         <f>X3+1</f>
         <v>120</v>
       </c>
-      <c r="Z3" s="20">
+      <c r="Z3">
         <f>Y3+1</f>
         <v>121</v>
       </c>
-      <c r="AA3" s="20">
+      <c r="AA3">
         <f>Z3+18</f>
         <v>139</v>
       </c>
-      <c r="AB3" s="20">
+      <c r="AB3">
         <f>AA3+1</f>
         <v>140</v>
       </c>
-      <c r="AC3" s="20">
+      <c r="AC3">
         <f>AB3+1</f>
         <v>141</v>
       </c>
-      <c r="AD3" s="20">
+      <c r="AD3">
         <f>AC3+18</f>
         <v>159</v>
       </c>
-      <c r="AE3" s="20">
+      <c r="AE3">
         <f>AD3+1</f>
         <v>160</v>
       </c>
-      <c r="AF3" s="20">
+      <c r="AF3">
         <f>AE3+1</f>
         <v>161</v>
       </c>
-      <c r="AG3" s="20">
+      <c r="AG3">
         <f>AF3+18</f>
         <v>179</v>
       </c>
-      <c r="AH3" s="20">
+      <c r="AH3">
         <f>AG3+1</f>
         <v>180</v>
       </c>
@@ -4603,39 +4601,39 @@
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="AZ3" s="21">
+      <c r="AZ3" s="3">
         <f t="shared" ref="AZ3:AZ5" si="1">Z3</f>
         <v>121</v>
       </c>
-      <c r="BA3" s="21">
+      <c r="BA3" s="3">
         <f t="shared" ref="BA3:BA5" si="2">AA3</f>
         <v>139</v>
       </c>
-      <c r="BB3" s="21">
+      <c r="BB3" s="3">
         <f t="shared" ref="BB3:BB5" si="3">AB3</f>
         <v>140</v>
       </c>
-      <c r="BC3" s="21">
+      <c r="BC3" s="3">
         <f t="shared" ref="BC3:BC5" si="4">AC3</f>
         <v>141</v>
       </c>
-      <c r="BD3" s="21">
+      <c r="BD3" s="3">
         <f t="shared" ref="BD3:BE5" si="5">AD3</f>
         <v>159</v>
       </c>
-      <c r="BE3" s="21">
+      <c r="BE3" s="3">
         <f t="shared" si="5"/>
         <v>160</v>
       </c>
-      <c r="BF3" s="21">
+      <c r="BF3" s="3">
         <f t="shared" ref="BF3:BF5" si="6">AF3</f>
         <v>161</v>
       </c>
-      <c r="BG3" s="21">
+      <c r="BG3" s="3">
         <f t="shared" ref="BG3:BG5" si="7">AG3</f>
         <v>179</v>
       </c>
-      <c r="BH3" s="21">
+      <c r="BH3" s="3">
         <f t="shared" ref="BH3:BH5" si="8">AH3</f>
         <v>180</v>
       </c>
@@ -4717,35 +4715,35 @@
         <f>W4</f>
         <v>1</v>
       </c>
-      <c r="AA4" s="20">
+      <c r="AA4">
         <f t="shared" ref="AA4:AE5" si="9">X4</f>
         <v>1.1100000000000001</v>
       </c>
-      <c r="AB4" s="20">
+      <c r="AB4">
         <f t="shared" si="9"/>
         <v>6.18</v>
       </c>
-      <c r="AC4" s="20">
+      <c r="AC4">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AD4" s="20">
+      <c r="AD4">
         <f t="shared" si="9"/>
         <v>1.1100000000000001</v>
       </c>
-      <c r="AE4" s="20">
+      <c r="AE4">
         <f t="shared" si="9"/>
         <v>6.18</v>
       </c>
-      <c r="AF4" s="20">
+      <c r="AF4">
         <f t="shared" ref="AF4:AF5" si="10">AC4</f>
         <v>1</v>
       </c>
-      <c r="AG4" s="20">
+      <c r="AG4">
         <f t="shared" ref="AG4:AG5" si="11">AD4</f>
         <v>1.1100000000000001</v>
       </c>
-      <c r="AH4" s="20">
+      <c r="AH4">
         <f t="shared" ref="AH4:AH5" si="12">AE4</f>
         <v>6.18</v>
       </c>
@@ -4813,39 +4811,39 @@
         <f t="shared" si="0"/>
         <v>6.18</v>
       </c>
-      <c r="AZ4" s="20">
+      <c r="AZ4">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="BA4" s="20">
+      <c r="BA4">
         <f t="shared" si="2"/>
         <v>1.1100000000000001</v>
       </c>
-      <c r="BB4" s="20">
+      <c r="BB4">
         <f t="shared" si="3"/>
         <v>6.18</v>
       </c>
-      <c r="BC4" s="20">
+      <c r="BC4">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="BD4" s="20">
+      <c r="BD4">
         <f t="shared" si="5"/>
         <v>1.1100000000000001</v>
       </c>
-      <c r="BE4" s="20">
+      <c r="BE4">
         <f t="shared" si="5"/>
         <v>6.18</v>
       </c>
-      <c r="BF4" s="20">
+      <c r="BF4">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="BG4" s="20">
+      <c r="BG4">
         <f t="shared" si="7"/>
         <v>1.1100000000000001</v>
       </c>
-      <c r="BH4" s="20">
+      <c r="BH4">
         <f t="shared" si="8"/>
         <v>6.18</v>
       </c>
@@ -4923,39 +4921,39 @@
       <c r="Y5">
         <v>10</v>
       </c>
-      <c r="Z5" s="20">
+      <c r="Z5">
         <f>W5</f>
         <v>1</v>
       </c>
-      <c r="AA5" s="20">
+      <c r="AA5">
         <f t="shared" si="9"/>
         <v>1.48</v>
       </c>
-      <c r="AB5" s="20">
+      <c r="AB5">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="AC5" s="20">
+      <c r="AC5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AD5" s="20">
+      <c r="AD5">
         <f t="shared" si="9"/>
         <v>1.48</v>
       </c>
-      <c r="AE5" s="20">
+      <c r="AE5">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="AF5" s="20">
+      <c r="AF5">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AG5" s="20">
+      <c r="AG5">
         <f t="shared" si="11"/>
         <v>1.48</v>
       </c>
-      <c r="AH5" s="20">
+      <c r="AH5">
         <f t="shared" si="12"/>
         <v>10</v>
       </c>
@@ -5023,39 +5021,39 @@
         <f t="shared" si="13"/>
         <v>10</v>
       </c>
-      <c r="AZ5" s="20">
+      <c r="AZ5">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="BA5" s="20">
+      <c r="BA5">
         <f t="shared" si="2"/>
         <v>1.48</v>
       </c>
-      <c r="BB5" s="20">
+      <c r="BB5">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="BC5" s="20">
+      <c r="BC5">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="BD5" s="20">
+      <c r="BD5">
         <f t="shared" si="5"/>
         <v>1.48</v>
       </c>
-      <c r="BE5" s="20">
+      <c r="BE5">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="BF5" s="20">
+      <c r="BF5">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="BG5" s="20">
+      <c r="BG5">
         <f t="shared" si="7"/>
         <v>1.48</v>
       </c>
-      <c r="BH5" s="20">
+      <c r="BH5">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
